--- a/main/ig/StructureDefinition-fr-human-name-document.xlsx
+++ b/main/ig/StructureDefinition-fr-human-name-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:53:23+00:00</t>
+    <t>2026-09-18T08:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-human-name-document.xlsx
+++ b/main/ig/StructureDefinition-fr-human-name-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:26:19+00:00</t>
+    <t>2026-09-24T07:33:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-human-name-document.xlsx
+++ b/main/ig/StructureDefinition-fr-human-name-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="168">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T07:33:45+00:00</t>
+    <t>2026-09-30T20:06:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name|2.2.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -347,7 +347,7 @@
     <t>assemblyOrder</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {humanname-assembly-order|5.3.0}
+    <t xml:space="preserve">Extension {humanname-assembly-order|5.2.0}
 </t>
   </si>
   <si>
@@ -380,6 +380,9 @@
   </si>
   <si>
     <t>required</t>
+  </si>
+  <si>
+    <t>The use of a human name.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
@@ -855,7 +858,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="22.015625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="80.25390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -1499,9 +1502,11 @@
       <c r="X6" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Y6" s="2"/>
+      <c r="Y6" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="Z6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>76</v>
@@ -1534,21 +1539,21 @@
         <v>84</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1574,16 +1579,16 @@
         <v>90</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O7" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P7" t="s" s="2">
         <v>76</v>
@@ -1632,7 +1637,7 @@
         <v>76</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>77</v>
@@ -1647,10 +1652,10 @@
         <v>84</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>76</v>
@@ -1658,14 +1663,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -1687,13 +1692,13 @@
         <v>90</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1743,7 +1748,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -1758,25 +1763,25 @@
         <v>84</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -1798,13 +1803,13 @@
         <v>90</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -1854,7 +1859,7 @@
         <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -1869,21 +1874,21 @@
         <v>84</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1909,10 +1914,10 @@
         <v>90</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1943,7 +1948,7 @@
       </c>
       <c r="Y10" s="2"/>
       <c r="Z10" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>76</v>
@@ -1961,7 +1966,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -1976,21 +1981,21 @@
         <v>84</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2016,10 +2021,10 @@
         <v>90</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2050,7 +2055,7 @@
       </c>
       <c r="Y11" s="2"/>
       <c r="Z11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>76</v>
@@ -2068,7 +2073,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2083,10 +2088,10 @@
         <v>84</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>76</v>
@@ -2094,10 +2099,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2120,17 +2125,17 @@
         <v>112</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>76</v>
@@ -2179,7 +2184,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2194,13 +2199,13 @@
         <v>84</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-fr-human-name-document.xlsx
+++ b/main/ig/StructureDefinition-fr-human-name-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T20:06:50+00:00</t>
+    <t>2026-10-01T08:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-human-name-document.xlsx
+++ b/main/ig/StructureDefinition-fr-human-name-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T08:49:37+00:00</t>
+    <t>2026-10-01T13:34:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-human-name-document.xlsx
+++ b/main/ig/StructureDefinition-fr-human-name-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:34:48+00:00</t>
+    <t>2026-10-05T07:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -347,7 +347,7 @@
     <t>assemblyOrder</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {humanname-assembly-order|5.2.0}
+    <t xml:space="preserve">Extension {humanname-assembly-order|5.3.0}
 </t>
   </si>
   <si>
